--- a/backtest_runs/20260410_193731/by_symbol/SGF/SGF.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SGF/SGF.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-947.8599999999981</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>99052.14</v>
@@ -633,7 +633,7 @@
         <v>-2626.599999999997</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>104465.22</v>
@@ -679,7 +679,7 @@
         <v>-10769.06000000001</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>93696.16</v>
@@ -771,7 +771,7 @@
         <v>-982.1199999999993</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>96082.94</v>
@@ -817,7 +817,7 @@
         <v>-2215.479999999997</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>93867.46000000001</v>
@@ -863,7 +863,7 @@
         <v>-194.1400000000019</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>93673.32000000001</v>
@@ -1001,7 +1001,7 @@
         <v>-3094.820000000009</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>92268.66</v>
@@ -1047,7 +1047,7 @@
         <v>-548.1600000000045</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>91720.5</v>
@@ -1093,7 +1093,7 @@
         <v>-1644.479999999997</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>90076.02</v>
@@ -1185,7 +1185,7 @@
         <v>-3894.219999999996</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>90567.08000000002</v>
@@ -1277,7 +1277,7 @@
         <v>-9912.559999999992</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>80928.60000000001</v>
@@ -1323,7 +1323,7 @@
         <v>-5698.580000000011</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>75230.02</v>
@@ -1415,7 +1415,7 @@
         <v>-1461.760000000001</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>78735.96000000002</v>
@@ -1461,7 +1461,7 @@
         <v>-1381.820000000009</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>77354.14</v>
